--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         <v>127735620</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,6 +889,1864 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128509248</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>764581</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7303540</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128509254</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>764533</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7303732</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128509252</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>764483</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7303618</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128509250</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>764482</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7303618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Upprörd varnade, födosök</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128509256</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>764541</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7303524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128509255</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>764610</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7303520</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128509244</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>764534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7303539</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128509243</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>764611</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7303524</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128509251</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>764687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7303547</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128509246</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>764618</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7303523</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128509245</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>764598</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7303542</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128509247</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>764491</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7303574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128528445</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>764494</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7303584</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128528442</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>764545</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7303533</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128528440</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>764751</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7303543</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128528443</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>764744</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7303557</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128528444</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>764495</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7303562</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128528441</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>764540</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7303533</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128528439</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58544</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Granberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>764588</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7303531</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R14" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R15" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R16" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R17" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128509248</v>
       </c>
       <c r="B4" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128509250</v>
       </c>
       <c r="B7" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R14" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R15" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2074,7 +2074,7 @@
         <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>128528439</v>
       </c>
       <c r="B22" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R16" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>80192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R17" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R14" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R15" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R16" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>80192</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R17" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R14" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R15" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,7 +2171,7 @@
         <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R14" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R15" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R16" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R17" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R14" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R15" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R16" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R17" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128509248</v>
       </c>
       <c r="B4" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128509250</v>
       </c>
       <c r="B7" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>128528439</v>
       </c>
       <c r="B22" t="n">
-        <v>58548</v>
+        <v>58575</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R16" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R17" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128509248</v>
       </c>
       <c r="B4" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128509250</v>
       </c>
       <c r="B7" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R14" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R15" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2074,7 +2074,7 @@
         <v>128528445</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128528442</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>128528439</v>
       </c>
       <c r="B22" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R14" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R15" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R16" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R17" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R16" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R17" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2748,6 +2748,324 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129001074</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80264</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öv Tväråsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>764672</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7303411</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129001078</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öv Tväråsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>764496</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7303586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129001075</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80258</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öv Tväråsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>764673</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7303410</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128509248</v>
       </c>
       <c r="B4" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128509250</v>
       </c>
       <c r="B7" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509245</v>
+        <v>128509247</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764598</v>
+        <v>764491</v>
       </c>
       <c r="R14" t="n">
-        <v>7303542</v>
+        <v>7303574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509247</v>
+        <v>128509245</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764491</v>
+        <v>764598</v>
       </c>
       <c r="R15" t="n">
-        <v>7303574</v>
+        <v>7303542</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R16" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R17" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>128528439</v>
       </c>
       <c r="B22" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>129001074</v>
       </c>
       <c r="B23" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129001075</v>
       </c>
       <c r="B25" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>128509254</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128509252</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128509256</v>
       </c>
       <c r="B8" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128509255</v>
       </c>
       <c r="B9" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128509244</v>
       </c>
       <c r="B10" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128509243</v>
       </c>
       <c r="B11" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128509251</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128509246</v>
       </c>
       <c r="B13" t="n">
-        <v>80170</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128509245</v>
       </c>
       <c r="B14" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128509247</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B16" t="n">
-        <v>98646</v>
+        <v>80139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R16" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528442</v>
+        <v>128528445</v>
       </c>
       <c r="B17" t="n">
-        <v>80134</v>
+        <v>98651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764545</v>
+        <v>764494</v>
       </c>
       <c r="R17" t="n">
-        <v>7303533</v>
+        <v>7303584</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>128528440</v>
       </c>
       <c r="B18" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128528443</v>
       </c>
       <c r="B19" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>128528444</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128528441</v>
       </c>
       <c r="B21" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2753,7 +2753,7 @@
         <v>129001074</v>
       </c>
       <c r="B23" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129001075</v>
       </c>
       <c r="B25" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2753,7 +2753,7 @@
         <v>129001074</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129001075</v>
       </c>
       <c r="B25" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2753,7 +2753,7 @@
         <v>129001074</v>
       </c>
       <c r="B23" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129001075</v>
       </c>
       <c r="B25" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,6 +3066,2869 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129411754</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>764721</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7303346</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>5×1m riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129411753</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>764631</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7303322</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129411755</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>764687</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7303363</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2×2m mycket riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129411767</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>764560</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7303562</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129411756</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>764666</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7303358</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129411747</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97576</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>764824</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7303549</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129411750</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>764715</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7303281</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129411766</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>764688</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7303588</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129411768</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>764664</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7303423</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129411748</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95931</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>764827</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7303569</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129411772</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>764582</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7303317</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129411751</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>764672</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7303387</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129411764</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>764686</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7303430</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2×5 m riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129411743</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>764626</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7303291</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129411761</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>764651</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7303425</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129411758</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>764675</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7303377</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129411769</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>764796</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7303480</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129411763</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>764668</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7303401</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1×2m</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129411749</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>764687</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7303270</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129411770</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>764812</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7303506</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129411757</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>764671</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7303368</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129411762</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>764665</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7303417</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2×7m riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129411765</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>764684</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7303436</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1×4 m riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129411746</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>764702</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7303366</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129411760</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>764659</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7303400</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129411773</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80181</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>764670</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7303409</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129411752</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>764672</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7303415</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129411759</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>764671</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7303388</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129411744</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90572</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Granberget ö, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>764812</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7303485</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,32 +3068,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411754</v>
+        <v>129411753</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>57831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>764721</v>
+        <v>764631</v>
       </c>
       <c r="R26" t="n">
-        <v>7303346</v>
+        <v>7303322</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5×1m riklig förekomst</t>
+          <t>Observerad</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,32 +3170,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129411753</v>
+        <v>129411754</v>
       </c>
       <c r="B27" t="n">
-        <v>57831</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>764631</v>
+        <v>764721</v>
       </c>
       <c r="R27" t="n">
-        <v>7303322</v>
+        <v>7303346</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Observerad</t>
+          <t>5×1m riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,7 +3275,7 @@
         <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>129411756</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>129411747</v>
       </c>
       <c r="B31" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>95931</v>
+        <v>95932</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4257,32 +4257,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411764</v>
+        <v>129411743</v>
       </c>
       <c r="B38" t="n">
-        <v>98705</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764686</v>
+        <v>764626</v>
       </c>
       <c r="R38" t="n">
-        <v>7303430</v>
+        <v>7303291</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4328,11 +4328,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,32 +4354,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411743</v>
+        <v>129411764</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>764626</v>
+        <v>764686</v>
       </c>
       <c r="R39" t="n">
-        <v>7303291</v>
+        <v>7303430</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4430,6 +4425,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R41" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R42" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4747,32 +4747,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129411763</v>
+        <v>129411749</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>764668</v>
+        <v>764687</v>
       </c>
       <c r="R43" t="n">
-        <v>7303401</v>
+        <v>7303270</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4818,11 +4818,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4849,10 +4844,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411749</v>
+        <v>129411770</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4855,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764687</v>
+        <v>764812</v>
       </c>
       <c r="R44" t="n">
-        <v>7303270</v>
+        <v>7303506</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4946,32 +4941,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411770</v>
+        <v>129411763</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764812</v>
+        <v>764668</v>
       </c>
       <c r="R45" t="n">
-        <v>7303506</v>
+        <v>7303401</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5017,6 +5012,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,32 +5344,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129411746</v>
+        <v>129411760</v>
       </c>
       <c r="B49" t="n">
-        <v>91551</v>
+        <v>98706</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>764702</v>
+        <v>764659</v>
       </c>
       <c r="R49" t="n">
-        <v>7303366</v>
+        <v>7303400</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5441,32 +5441,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129411760</v>
+        <v>129411746</v>
       </c>
       <c r="B50" t="n">
-        <v>98705</v>
+        <v>91551</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>764659</v>
+        <v>764702</v>
       </c>
       <c r="R50" t="n">
-        <v>7303400</v>
+        <v>7303366</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5732,32 +5732,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129411759</v>
+        <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>98705</v>
+        <v>90572</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>764671</v>
+        <v>764812</v>
       </c>
       <c r="R53" t="n">
-        <v>7303388</v>
+        <v>7303485</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5803,11 +5803,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5834,32 +5829,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129411744</v>
+        <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>90572</v>
+        <v>98706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>764812</v>
+        <v>764671</v>
       </c>
       <c r="R54" t="n">
-        <v>7303485</v>
+        <v>7303388</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5905,6 +5900,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -2753,7 +2753,7 @@
         <v>129001074</v>
       </c>
       <c r="B23" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>129001078</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129001075</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>129411754</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>129411767</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>129411756</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B31" t="n">
-        <v>97577</v>
+        <v>80148</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R31" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3644,11 +3644,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411750</v>
+        <v>129411747</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>97581</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764715</v>
+        <v>764824</v>
       </c>
       <c r="R32" t="n">
-        <v>7303281</v>
+        <v>7303549</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3746,6 +3741,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,7 +3775,7 @@
         <v>129411766</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>129411768</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>95932</v>
+        <v>95936</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4063,32 +4063,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411772</v>
+        <v>129411751</v>
       </c>
       <c r="B36" t="n">
-        <v>92822</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>764582</v>
+        <v>764672</v>
       </c>
       <c r="R36" t="n">
-        <v>7303317</v>
+        <v>7303387</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411751</v>
+        <v>129411743</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>79662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764672</v>
+        <v>764626</v>
       </c>
       <c r="R37" t="n">
-        <v>7303387</v>
+        <v>7303291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4257,32 +4257,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411743</v>
+        <v>129411764</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764626</v>
+        <v>764686</v>
       </c>
       <c r="R38" t="n">
-        <v>7303291</v>
+        <v>7303430</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4328,6 +4328,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,32 +4359,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411764</v>
+        <v>129411772</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4389,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>764686</v>
+        <v>764582</v>
       </c>
       <c r="R39" t="n">
-        <v>7303430</v>
+        <v>7303317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4425,11 +4430,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R41" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B42" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R42" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4750,7 +4750,7 @@
         <v>129411749</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>129411770</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>129411763</v>
       </c>
       <c r="B45" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,32 +5344,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129411760</v>
+        <v>129411746</v>
       </c>
       <c r="B49" t="n">
-        <v>98706</v>
+        <v>91554</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>764659</v>
+        <v>764702</v>
       </c>
       <c r="R49" t="n">
-        <v>7303400</v>
+        <v>7303366</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5441,32 +5441,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129411746</v>
+        <v>129411760</v>
       </c>
       <c r="B50" t="n">
-        <v>91551</v>
+        <v>98710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>764702</v>
+        <v>764659</v>
       </c>
       <c r="R50" t="n">
-        <v>7303366</v>
+        <v>7303400</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5541,7 +5541,7 @@
         <v>129411773</v>
       </c>
       <c r="B51" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>129411752</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3068,32 +3068,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411753</v>
+        <v>129411754</v>
       </c>
       <c r="B26" t="n">
-        <v>57834</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>764631</v>
+        <v>764721</v>
       </c>
       <c r="R26" t="n">
-        <v>7303322</v>
+        <v>7303346</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Observerad</t>
+          <t>5×1m riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129411754</v>
+        <v>129411755</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>764721</v>
+        <v>764687</v>
       </c>
       <c r="R27" t="n">
-        <v>7303346</v>
+        <v>7303363</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>5×1m riklig förekomst</t>
+          <t>2×2m mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,32 +3272,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129411755</v>
+        <v>129411753</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>57839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>764687</v>
+        <v>764631</v>
       </c>
       <c r="R28" t="n">
-        <v>7303363</v>
+        <v>7303322</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2×2m mycket riklig förekomst</t>
+          <t>Observerad</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,7 +3377,7 @@
         <v>129411767</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411750</v>
+        <v>129411756</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764715</v>
+        <v>764666</v>
       </c>
       <c r="R30" t="n">
-        <v>7303281</v>
+        <v>7303358</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3542,6 +3542,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3568,32 +3573,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411756</v>
+        <v>129411750</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764666</v>
+        <v>764715</v>
       </c>
       <c r="R31" t="n">
-        <v>7303358</v>
+        <v>7303281</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3639,11 +3644,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3673,7 +3673,7 @@
         <v>129411747</v>
       </c>
       <c r="B32" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>129411766</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>129411768</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129411772</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411743</v>
+        <v>129411751</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>80180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764626</v>
+        <v>764672</v>
       </c>
       <c r="R37" t="n">
-        <v>7303291</v>
+        <v>7303387</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4257,10 +4257,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411751</v>
+        <v>129411743</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>79694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4268,21 +4268,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764672</v>
+        <v>764626</v>
       </c>
       <c r="R38" t="n">
-        <v>7303387</v>
+        <v>7303291</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4357,7 +4357,7 @@
         <v>129411764</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R41" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R42" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4747,32 +4747,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129411763</v>
+        <v>129411770</v>
       </c>
       <c r="B43" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>764668</v>
+        <v>764812</v>
       </c>
       <c r="R43" t="n">
-        <v>7303401</v>
+        <v>7303506</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4818,11 +4818,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4852,7 +4847,7 @@
         <v>129411749</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4946,32 +4941,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411770</v>
+        <v>129411763</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764812</v>
+        <v>764668</v>
       </c>
       <c r="R45" t="n">
-        <v>7303506</v>
+        <v>7303401</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5017,6 +5012,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129411760</v>
       </c>
       <c r="B49" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129411746</v>
       </c>
       <c r="B50" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>129411773</v>
       </c>
       <c r="B51" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>129411752</v>
       </c>
       <c r="B52" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5732,32 +5732,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129411744</v>
+        <v>129411759</v>
       </c>
       <c r="B53" t="n">
-        <v>90613</v>
+        <v>98768</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>764812</v>
+        <v>764671</v>
       </c>
       <c r="R53" t="n">
-        <v>7303485</v>
+        <v>7303388</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5803,6 +5803,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5829,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129411759</v>
+        <v>129411744</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>90619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>764671</v>
+        <v>764812</v>
       </c>
       <c r="R54" t="n">
-        <v>7303388</v>
+        <v>7303485</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5900,11 +5905,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3068,32 +3068,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411754</v>
+        <v>129411753</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>57840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>764721</v>
+        <v>764631</v>
       </c>
       <c r="R26" t="n">
-        <v>7303346</v>
+        <v>7303322</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5×1m riklig förekomst</t>
+          <t>Observerad</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129411755</v>
+        <v>129411754</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>764687</v>
+        <v>764721</v>
       </c>
       <c r="R27" t="n">
-        <v>7303363</v>
+        <v>7303346</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2×2m mycket riklig förekomst</t>
+          <t>5×1m riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,32 +3272,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129411753</v>
+        <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>57839</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>764631</v>
+        <v>764687</v>
       </c>
       <c r="R28" t="n">
-        <v>7303322</v>
+        <v>7303363</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Observerad</t>
+          <t>2×2m mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,7 +3377,7 @@
         <v>129411767</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>129411756</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411750</v>
+        <v>129411747</v>
       </c>
       <c r="B31" t="n">
-        <v>80180</v>
+        <v>97640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764715</v>
+        <v>764824</v>
       </c>
       <c r="R31" t="n">
-        <v>7303281</v>
+        <v>7303549</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3644,6 +3644,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,32 +3675,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B32" t="n">
-        <v>97639</v>
+        <v>80181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R32" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3741,11 +3746,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,7 +3775,7 @@
         <v>129411766</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>129411768</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129411772</v>
       </c>
       <c r="B36" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>129411751</v>
       </c>
       <c r="B37" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>129411743</v>
       </c>
       <c r="B38" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>129411764</v>
       </c>
       <c r="B39" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R41" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R42" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4747,32 +4747,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129411770</v>
+        <v>129411763</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>764812</v>
+        <v>764668</v>
       </c>
       <c r="R43" t="n">
-        <v>7303506</v>
+        <v>7303401</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4818,6 +4818,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4847,7 +4852,7 @@
         <v>129411749</v>
       </c>
       <c r="B44" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4941,32 +4946,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411763</v>
+        <v>129411770</v>
       </c>
       <c r="B45" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764668</v>
+        <v>764812</v>
       </c>
       <c r="R45" t="n">
-        <v>7303401</v>
+        <v>7303506</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5012,11 +5017,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129411760</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129411746</v>
       </c>
       <c r="B50" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>129411773</v>
       </c>
       <c r="B51" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>129411752</v>
       </c>
       <c r="B52" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5732,32 +5732,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129411759</v>
+        <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>98768</v>
+        <v>90620</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>764671</v>
+        <v>764812</v>
       </c>
       <c r="R53" t="n">
-        <v>7303388</v>
+        <v>7303485</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5803,11 +5803,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5834,32 +5829,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129411744</v>
+        <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>90619</v>
+        <v>98769</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>764812</v>
+        <v>764671</v>
       </c>
       <c r="R54" t="n">
-        <v>7303485</v>
+        <v>7303388</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5905,6 +5900,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411756</v>
+        <v>129411750</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764666</v>
+        <v>764715</v>
       </c>
       <c r="R30" t="n">
-        <v>7303358</v>
+        <v>7303281</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3542,11 +3542,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411750</v>
+        <v>129411756</v>
       </c>
       <c r="B32" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764715</v>
+        <v>764666</v>
       </c>
       <c r="R32" t="n">
-        <v>7303281</v>
+        <v>7303358</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3746,6 +3741,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R41" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B42" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R42" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3173,7 +3173,7 @@
         <v>129411754</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>129411767</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411750</v>
+        <v>129411756</v>
       </c>
       <c r="B30" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764715</v>
+        <v>764666</v>
       </c>
       <c r="R30" t="n">
-        <v>7303281</v>
+        <v>7303358</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3542,6 +3542,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3568,32 +3573,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B31" t="n">
-        <v>97640</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R31" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3639,11 +3644,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411756</v>
+        <v>129411747</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>97645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764666</v>
+        <v>764824</v>
       </c>
       <c r="R32" t="n">
-        <v>7303358</v>
+        <v>7303549</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2×4m riklig förekomst</t>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,7 +3775,7 @@
         <v>129411766</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>129411768</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129411772</v>
       </c>
       <c r="B36" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>129411751</v>
       </c>
       <c r="B37" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>129411743</v>
       </c>
       <c r="B38" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>129411764</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R41" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R42" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4750,7 +4750,7 @@
         <v>129411763</v>
       </c>
       <c r="B43" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>129411749</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>129411770</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129411760</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129411746</v>
       </c>
       <c r="B50" t="n">
-        <v>91599</v>
+        <v>91604</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>129411773</v>
       </c>
       <c r="B51" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>129411752</v>
       </c>
       <c r="B52" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411756</v>
+        <v>129411747</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764666</v>
+        <v>764824</v>
       </c>
       <c r="R30" t="n">
-        <v>7303358</v>
+        <v>7303549</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2×4m riklig förekomst</t>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3573,32 +3573,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411750</v>
+        <v>129411756</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764715</v>
+        <v>764666</v>
       </c>
       <c r="R31" t="n">
-        <v>7303281</v>
+        <v>7303358</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3644,6 +3644,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,32 +3675,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B32" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R32" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3741,11 +3746,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,32 +4063,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411772</v>
+        <v>129411751</v>
       </c>
       <c r="B36" t="n">
-        <v>92875</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>764582</v>
+        <v>764672</v>
       </c>
       <c r="R36" t="n">
-        <v>7303317</v>
+        <v>7303387</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411751</v>
+        <v>129411743</v>
       </c>
       <c r="B37" t="n">
-        <v>80186</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764672</v>
+        <v>764626</v>
       </c>
       <c r="R37" t="n">
-        <v>7303387</v>
+        <v>7303291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4257,32 +4257,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411743</v>
+        <v>129411772</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764626</v>
+        <v>764582</v>
       </c>
       <c r="R38" t="n">
-        <v>7303291</v>
+        <v>7303317</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4747,32 +4747,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129411763</v>
+        <v>129411749</v>
       </c>
       <c r="B43" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>764668</v>
+        <v>764687</v>
       </c>
       <c r="R43" t="n">
-        <v>7303401</v>
+        <v>7303270</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4818,11 +4818,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4849,32 +4844,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411749</v>
+        <v>129411763</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764687</v>
+        <v>764668</v>
       </c>
       <c r="R44" t="n">
-        <v>7303270</v>
+        <v>7303401</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4920,6 +4915,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5344,32 +5344,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129411760</v>
+        <v>129411746</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>91604</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>764659</v>
+        <v>764702</v>
       </c>
       <c r="R49" t="n">
-        <v>7303400</v>
+        <v>7303366</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5441,32 +5441,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129411746</v>
+        <v>129411760</v>
       </c>
       <c r="B50" t="n">
-        <v>91604</v>
+        <v>98774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>764702</v>
+        <v>764659</v>
       </c>
       <c r="R50" t="n">
-        <v>7303366</v>
+        <v>7303400</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5732,32 +5732,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129411744</v>
+        <v>129411759</v>
       </c>
       <c r="B53" t="n">
-        <v>90625</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>764812</v>
+        <v>764671</v>
       </c>
       <c r="R53" t="n">
-        <v>7303485</v>
+        <v>7303388</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5803,6 +5803,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5829,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129411759</v>
+        <v>129411744</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>90625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>764671</v>
+        <v>764812</v>
       </c>
       <c r="R54" t="n">
-        <v>7303388</v>
+        <v>7303485</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5900,11 +5905,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3068,32 +3068,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411753</v>
+        <v>129411754</v>
       </c>
       <c r="B26" t="n">
-        <v>57840</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>764631</v>
+        <v>764721</v>
       </c>
       <c r="R26" t="n">
-        <v>7303322</v>
+        <v>7303346</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Observerad</t>
+          <t>5×1m riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,7 +3170,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129411754</v>
+        <v>129411755</v>
       </c>
       <c r="B27" t="n">
         <v>98774</v>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>764721</v>
+        <v>764687</v>
       </c>
       <c r="R27" t="n">
-        <v>7303346</v>
+        <v>7303363</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>5×1m riklig förekomst</t>
+          <t>2×2m mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,32 +3272,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129411755</v>
+        <v>129411753</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>57840</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>764687</v>
+        <v>764631</v>
       </c>
       <c r="R28" t="n">
-        <v>7303363</v>
+        <v>7303322</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2×2m mycket riklig förekomst</t>
+          <t>Observerad</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B30" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R30" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3542,11 +3542,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411750</v>
+        <v>129411747</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>97645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764715</v>
+        <v>764824</v>
       </c>
       <c r="R32" t="n">
-        <v>7303281</v>
+        <v>7303549</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3746,6 +3741,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,32 +4063,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411751</v>
+        <v>129411772</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>92875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>764672</v>
+        <v>764582</v>
       </c>
       <c r="R36" t="n">
-        <v>7303387</v>
+        <v>7303317</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411743</v>
+        <v>129411751</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>80186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764626</v>
+        <v>764672</v>
       </c>
       <c r="R37" t="n">
-        <v>7303291</v>
+        <v>7303387</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4257,32 +4257,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411772</v>
+        <v>129411743</v>
       </c>
       <c r="B38" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764582</v>
+        <v>764626</v>
       </c>
       <c r="R38" t="n">
-        <v>7303317</v>
+        <v>7303291</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4844,32 +4844,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411763</v>
+        <v>129411770</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764668</v>
+        <v>764812</v>
       </c>
       <c r="R44" t="n">
-        <v>7303401</v>
+        <v>7303506</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4915,11 +4915,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,32 +4941,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411770</v>
+        <v>129411763</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764812</v>
+        <v>764668</v>
       </c>
       <c r="R45" t="n">
-        <v>7303506</v>
+        <v>7303401</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5017,6 +5012,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5732,32 +5732,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129411759</v>
+        <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>90625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>764671</v>
+        <v>764812</v>
       </c>
       <c r="R53" t="n">
-        <v>7303388</v>
+        <v>7303485</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5803,11 +5803,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5834,32 +5829,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129411744</v>
+        <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>90625</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>764812</v>
+        <v>764671</v>
       </c>
       <c r="R54" t="n">
-        <v>7303485</v>
+        <v>7303388</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5905,6 +5900,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3068,32 +3068,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411754</v>
+        <v>129411753</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>57840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>764721</v>
+        <v>764631</v>
       </c>
       <c r="R26" t="n">
-        <v>7303346</v>
+        <v>7303322</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5×1m riklig förekomst</t>
+          <t>Observerad</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,7 +3170,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129411755</v>
+        <v>129411754</v>
       </c>
       <c r="B27" t="n">
         <v>98774</v>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>764687</v>
+        <v>764721</v>
       </c>
       <c r="R27" t="n">
-        <v>7303363</v>
+        <v>7303346</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2×2m mycket riklig förekomst</t>
+          <t>5×1m riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,32 +3272,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129411753</v>
+        <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>57840</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>764631</v>
+        <v>764687</v>
       </c>
       <c r="R28" t="n">
-        <v>7303322</v>
+        <v>7303363</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Observerad</t>
+          <t>2×2m mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411750</v>
+        <v>129411747</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>97645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764715</v>
+        <v>764824</v>
       </c>
       <c r="R30" t="n">
-        <v>7303281</v>
+        <v>7303549</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3542,6 +3542,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3670,32 +3675,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B32" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R32" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3741,11 +3746,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411751</v>
+        <v>129411743</v>
       </c>
       <c r="B37" t="n">
-        <v>80186</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764672</v>
+        <v>764626</v>
       </c>
       <c r="R37" t="n">
-        <v>7303387</v>
+        <v>7303291</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4257,10 +4257,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411743</v>
+        <v>129411751</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4268,21 +4268,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764626</v>
+        <v>764672</v>
       </c>
       <c r="R38" t="n">
-        <v>7303291</v>
+        <v>7303387</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4844,32 +4844,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411770</v>
+        <v>129411763</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764812</v>
+        <v>764668</v>
       </c>
       <c r="R44" t="n">
-        <v>7303506</v>
+        <v>7303401</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4915,6 +4915,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4941,32 +4946,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411763</v>
+        <v>129411770</v>
       </c>
       <c r="B45" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764668</v>
+        <v>764812</v>
       </c>
       <c r="R45" t="n">
-        <v>7303401</v>
+        <v>7303506</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5012,11 +5017,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3173,7 +3173,7 @@
         <v>129411754</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>129411747</v>
       </c>
       <c r="B30" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411756</v>
+        <v>129411750</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764666</v>
+        <v>764715</v>
       </c>
       <c r="R31" t="n">
-        <v>7303358</v>
+        <v>7303281</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3644,11 +3644,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411750</v>
+        <v>129411756</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764715</v>
+        <v>764666</v>
       </c>
       <c r="R32" t="n">
-        <v>7303281</v>
+        <v>7303358</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3746,6 +3741,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4063,32 +4063,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411772</v>
+        <v>129411751</v>
       </c>
       <c r="B36" t="n">
-        <v>92875</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>764582</v>
+        <v>764672</v>
       </c>
       <c r="R36" t="n">
-        <v>7303317</v>
+        <v>7303387</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4257,32 +4257,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411751</v>
+        <v>129411764</v>
       </c>
       <c r="B38" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764672</v>
+        <v>764686</v>
       </c>
       <c r="R38" t="n">
-        <v>7303387</v>
+        <v>7303430</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4328,6 +4328,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,32 +4359,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411764</v>
+        <v>129411772</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>92879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4389,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>764686</v>
+        <v>764582</v>
       </c>
       <c r="R39" t="n">
-        <v>7303430</v>
+        <v>7303317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4425,11 +4430,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R41" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R42" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4747,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129411749</v>
+        <v>129411770</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,21 +4758,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>764687</v>
+        <v>764812</v>
       </c>
       <c r="R43" t="n">
-        <v>7303270</v>
+        <v>7303506</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4844,32 +4844,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411763</v>
+        <v>129411749</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764668</v>
+        <v>764687</v>
       </c>
       <c r="R44" t="n">
-        <v>7303401</v>
+        <v>7303270</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4915,11 +4915,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,32 +4941,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411770</v>
+        <v>129411763</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764812</v>
+        <v>764668</v>
       </c>
       <c r="R45" t="n">
-        <v>7303506</v>
+        <v>7303401</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5017,6 +5012,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129411746</v>
       </c>
       <c r="B49" t="n">
-        <v>91604</v>
+        <v>91608</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129411760</v>
       </c>
       <c r="B50" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -3173,7 +3173,7 @@
         <v>129411754</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>129411755</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,32 +3471,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411747</v>
+        <v>129411750</v>
       </c>
       <c r="B30" t="n">
-        <v>97649</v>
+        <v>80186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764824</v>
+        <v>764715</v>
       </c>
       <c r="R30" t="n">
-        <v>7303549</v>
+        <v>7303281</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3542,11 +3542,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3573,32 +3568,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411750</v>
+        <v>129411756</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3608,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764715</v>
+        <v>764666</v>
       </c>
       <c r="R31" t="n">
-        <v>7303281</v>
+        <v>7303358</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3644,6 +3639,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411756</v>
+        <v>129411747</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>97651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764666</v>
+        <v>764824</v>
       </c>
       <c r="R32" t="n">
-        <v>7303358</v>
+        <v>7303549</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2×4m riklig förekomst</t>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,7 +3969,7 @@
         <v>129411748</v>
       </c>
       <c r="B35" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4063,32 +4063,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411751</v>
+        <v>129411764</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>764672</v>
+        <v>764686</v>
       </c>
       <c r="R36" t="n">
-        <v>7303387</v>
+        <v>7303430</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4134,6 +4134,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4160,32 +4165,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411743</v>
+        <v>129411772</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764626</v>
+        <v>764582</v>
       </c>
       <c r="R37" t="n">
-        <v>7303291</v>
+        <v>7303317</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4257,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411764</v>
+        <v>129411751</v>
       </c>
       <c r="B38" t="n">
-        <v>98778</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764686</v>
+        <v>764672</v>
       </c>
       <c r="R38" t="n">
-        <v>7303430</v>
+        <v>7303387</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4328,11 +4333,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,32 +4359,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411772</v>
+        <v>129411743</v>
       </c>
       <c r="B39" t="n">
-        <v>92879</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>764582</v>
+        <v>764626</v>
       </c>
       <c r="R39" t="n">
-        <v>7303317</v>
+        <v>7303291</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4459,7 +4459,7 @@
         <v>129411761</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411758</v>
+        <v>129411769</v>
       </c>
       <c r="B41" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764675</v>
+        <v>764796</v>
       </c>
       <c r="R41" t="n">
-        <v>7303377</v>
+        <v>7303480</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411769</v>
+        <v>129411758</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764796</v>
+        <v>764675</v>
       </c>
       <c r="R42" t="n">
-        <v>7303480</v>
+        <v>7303377</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4844,32 +4844,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411749</v>
+        <v>129411763</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764687</v>
+        <v>764668</v>
       </c>
       <c r="R44" t="n">
-        <v>7303270</v>
+        <v>7303401</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4915,6 +4915,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4941,32 +4946,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411763</v>
+        <v>129411749</v>
       </c>
       <c r="B45" t="n">
-        <v>98778</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764668</v>
+        <v>764687</v>
       </c>
       <c r="R45" t="n">
-        <v>7303401</v>
+        <v>7303270</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5012,11 +5017,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5046,7 +5046,7 @@
         <v>129411757</v>
       </c>
       <c r="B46" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129411762</v>
       </c>
       <c r="B47" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>129411765</v>
       </c>
       <c r="B48" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,32 +5344,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129411746</v>
+        <v>129411760</v>
       </c>
       <c r="B49" t="n">
-        <v>91608</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>764702</v>
+        <v>764659</v>
       </c>
       <c r="R49" t="n">
-        <v>7303366</v>
+        <v>7303400</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5441,32 +5441,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129411760</v>
+        <v>129411746</v>
       </c>
       <c r="B50" t="n">
-        <v>98778</v>
+        <v>91610</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>764659</v>
+        <v>764702</v>
       </c>
       <c r="R50" t="n">
-        <v>7303400</v>
+        <v>7303366</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5735,7 +5735,7 @@
         <v>129411744</v>
       </c>
       <c r="B53" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>129411759</v>
       </c>
       <c r="B54" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820678</v>
+        <v>129411746</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öv Tväråsel, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>764656</v>
+        <v>764702</v>
       </c>
       <c r="R2" t="n">
-        <v>7303264</v>
+        <v>7303366</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,64 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127735620</v>
+        <v>129411744</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öv Tväråsel, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764677</v>
+        <v>764812</v>
       </c>
       <c r="R3" t="n">
-        <v>7303376</v>
+        <v>7303485</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,57 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128509248</v>
+        <v>129411748</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764581</v>
+        <v>764827</v>
       </c>
       <c r="R4" t="n">
-        <v>7303540</v>
+        <v>7303569</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128509254</v>
+        <v>129411772</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>764533</v>
+        <v>764582</v>
       </c>
       <c r="R5" t="n">
-        <v>7303732</v>
+        <v>7303317</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1054,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128509252</v>
+        <v>128509251</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1121,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764483</v>
+        <v>764687</v>
       </c>
       <c r="R6" t="n">
-        <v>7303618</v>
+        <v>7303547</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128509250</v>
+        <v>128509252</v>
       </c>
       <c r="B7" t="n">
-        <v>56904</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,7 +1195,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764482</v>
+        <v>764483</v>
       </c>
       <c r="R7" t="n">
         <v>7303618</v>
@@ -1254,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Upprörd varnade, födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,27 +1257,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128509256</v>
+        <v>128509254</v>
       </c>
       <c r="B8" t="n">
-        <v>80174</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1320,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>764541</v>
+        <v>764533</v>
       </c>
       <c r="R8" t="n">
-        <v>7303524</v>
+        <v>7303732</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1382,27 +1354,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128509255</v>
+        <v>129411766</v>
       </c>
       <c r="B9" t="n">
-        <v>80174</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1413,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>764610</v>
+        <v>764688</v>
       </c>
       <c r="R9" t="n">
-        <v>7303520</v>
+        <v>7303588</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1447,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128509244</v>
+        <v>129411767</v>
       </c>
       <c r="B10" t="n">
-        <v>97522</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>764534</v>
+        <v>764560</v>
       </c>
       <c r="R10" t="n">
-        <v>7303539</v>
+        <v>7303562</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,45 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128509243</v>
+        <v>129411768</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>764611</v>
+        <v>764664</v>
       </c>
       <c r="R11" t="n">
-        <v>7303524</v>
+        <v>7303423</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128509251</v>
+        <v>129411769</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1704,14 +1676,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>764687</v>
+        <v>764796</v>
       </c>
       <c r="R12" t="n">
-        <v>7303547</v>
+        <v>7303480</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,45 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128509246</v>
+        <v>129411770</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>764618</v>
+        <v>764812</v>
       </c>
       <c r="R13" t="n">
-        <v>7303523</v>
+        <v>7303506</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128509245</v>
+        <v>129411743</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764598</v>
+        <v>764626</v>
       </c>
       <c r="R14" t="n">
-        <v>7303542</v>
+        <v>7303291</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1932,17 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,48 +1936,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128509247</v>
+        <v>119820678</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>granberget, Nb</t>
+          <t>Öv Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764491</v>
+        <v>764656</v>
       </c>
       <c r="R15" t="n">
-        <v>7303574</v>
+        <v>7303264</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,17 +2005,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Frodiga, storvuxna, rikligt bestånd</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2059,22 +2030,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128528442</v>
+        <v>128509245</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,17 +2073,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Granberget, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>764545</v>
+        <v>764598</v>
       </c>
       <c r="R16" t="n">
-        <v>7303533</v>
+        <v>7303542</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2142,6 +2113,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2156,44 +2132,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128528445</v>
+        <v>128528442</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2203,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>764494</v>
+        <v>764545</v>
       </c>
       <c r="R17" t="n">
-        <v>7303584</v>
+        <v>7303533</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2265,32 +2241,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128528440</v>
+        <v>128528443</v>
       </c>
       <c r="B18" t="n">
-        <v>80168</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2300,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>764751</v>
+        <v>764744</v>
       </c>
       <c r="R18" t="n">
-        <v>7303543</v>
+        <v>7303557</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2362,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128528443</v>
+        <v>129411749</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2393,17 +2369,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>764744</v>
+        <v>764687</v>
       </c>
       <c r="R19" t="n">
-        <v>7303557</v>
+        <v>7303270</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2427,12 +2403,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2447,60 +2423,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128528444</v>
+        <v>129411750</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>764495</v>
+        <v>764715</v>
       </c>
       <c r="R20" t="n">
-        <v>7303562</v>
+        <v>7303281</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2524,12 +2500,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,60 +2520,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128528441</v>
+        <v>129411751</v>
       </c>
       <c r="B21" t="n">
-        <v>80168</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>764540</v>
+        <v>764672</v>
       </c>
       <c r="R21" t="n">
-        <v>7303533</v>
+        <v>7303387</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2621,12 +2597,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2641,60 +2617,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128528439</v>
+        <v>129411752</v>
       </c>
       <c r="B22" t="n">
-        <v>58582</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granberget, Nb</t>
+          <t>Granberget ö, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>764588</v>
+        <v>764672</v>
       </c>
       <c r="R22" t="n">
-        <v>7303531</v>
+        <v>7303415</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2718,12 +2694,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2738,22 +2714,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129001074</v>
+        <v>128509243</v>
       </c>
       <c r="B23" t="n">
-        <v>80184</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,41 +2737,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öv Tväråsel, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>764672</v>
+        <v>764611</v>
       </c>
       <c r="R23" t="n">
-        <v>7303411</v>
+        <v>7303524</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2819,17 +2791,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,64 +2811,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129001078</v>
+        <v>128528440</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öv Tväråsel, Nb</t>
+          <t>Granberget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>764496</v>
+        <v>764751</v>
       </c>
       <c r="R24" t="n">
-        <v>7303586</v>
+        <v>7303543</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2925,17 +2888,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2950,22 +2908,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129001075</v>
+        <v>128528441</v>
       </c>
       <c r="B25" t="n">
-        <v>80178</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2990,24 +2948,20 @@
           <t>(Spreng.) Tuck.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öv Tväråsel, Nb</t>
+          <t>Granberget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>764673</v>
+        <v>764540</v>
       </c>
       <c r="R25" t="n">
-        <v>7303410</v>
+        <v>7303533</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3031,17 +2985,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3056,22 +3005,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129411753</v>
+        <v>129001075</v>
       </c>
       <c r="B26" t="n">
-        <v>57840</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,37 +3028,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Öv Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>764631</v>
+        <v>764673</v>
       </c>
       <c r="R26" t="n">
-        <v>7303322</v>
+        <v>7303410</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3133,17 +3086,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Observerad</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3158,57 +3111,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129411754</v>
+        <v>128509255</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>764721</v>
+        <v>764610</v>
       </c>
       <c r="R27" t="n">
-        <v>7303346</v>
+        <v>7303520</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3235,17 +3188,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>5×1m riklig förekomst</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,45 +3220,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129411755</v>
+        <v>128509256</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>764687</v>
+        <v>764541</v>
       </c>
       <c r="R28" t="n">
-        <v>7303363</v>
+        <v>7303524</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3337,17 +3285,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2×2m mycket riklig förekomst</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3374,27 +3317,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129411767</v>
+        <v>129001074</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3402,20 +3345,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Öv Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>764560</v>
+        <v>764672</v>
       </c>
       <c r="R29" t="n">
-        <v>7303562</v>
+        <v>7303411</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3439,12 +3386,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3459,44 +3411,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129411750</v>
+        <v>129411773</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>80467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>764715</v>
+        <v>764670</v>
       </c>
       <c r="R30" t="n">
-        <v>7303281</v>
+        <v>7303409</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3568,45 +3520,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129411756</v>
+        <v>128509246</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>764666</v>
+        <v>764618</v>
       </c>
       <c r="R31" t="n">
-        <v>7303358</v>
+        <v>7303523</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3633,17 +3585,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2×4m riklig förekomst</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129411747</v>
+        <v>128509248</v>
       </c>
       <c r="B32" t="n">
-        <v>97651</v>
+        <v>57132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3681,34 +3628,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>764824</v>
+        <v>764581</v>
       </c>
       <c r="R32" t="n">
-        <v>7303549</v>
+        <v>7303540</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3735,17 +3682,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3772,45 +3714,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129411766</v>
+        <v>128509250</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>57132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>764688</v>
+        <v>764482</v>
       </c>
       <c r="R33" t="n">
-        <v>7303588</v>
+        <v>7303618</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3837,12 +3779,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Upprörd varnade, födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,10 +3816,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129411768</v>
+        <v>129411753</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>58057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3827,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3851,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>764664</v>
+        <v>764631</v>
       </c>
       <c r="R34" t="n">
-        <v>7303423</v>
+        <v>7303322</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3940,6 +3887,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Observerad</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,10 +3918,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129411748</v>
+        <v>128528439</v>
       </c>
       <c r="B35" t="n">
-        <v>96006</v>
+        <v>58817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,37 +3929,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2809</v>
+        <v>208249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Granberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>764827</v>
+        <v>764588</v>
       </c>
       <c r="R35" t="n">
-        <v>7303569</v>
+        <v>7303531</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4031,12 +3983,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4051,22 +4003,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129411764</v>
+        <v>127735620</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,20 +4043,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Öv Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>764686</v>
+        <v>764677</v>
       </c>
       <c r="R36" t="n">
-        <v>7303430</v>
+        <v>7303376</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4128,17 +4084,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>2×5 m riklig förekomst</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4153,57 +4109,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129411772</v>
+        <v>128509247</v>
       </c>
       <c r="B37" t="n">
-        <v>92881</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>764582</v>
+        <v>764491</v>
       </c>
       <c r="R37" t="n">
-        <v>7303317</v>
+        <v>7303574</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4230,12 +4186,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Frodiga, storvuxna, rikligt bestånd</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4262,48 +4223,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129411751</v>
+        <v>128528444</v>
       </c>
       <c r="B38" t="n">
-        <v>80186</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Granberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>764672</v>
+        <v>764495</v>
       </c>
       <c r="R38" t="n">
-        <v>7303387</v>
+        <v>7303562</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4327,12 +4288,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4347,60 +4308,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129411743</v>
+        <v>128528445</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Granberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>764626</v>
+        <v>764494</v>
       </c>
       <c r="R39" t="n">
-        <v>7303291</v>
+        <v>7303584</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4424,12 +4385,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4444,22 +4405,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129411761</v>
+        <v>129001078</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4484,20 +4445,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>Öv Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>764651</v>
+        <v>764496</v>
       </c>
       <c r="R40" t="n">
-        <v>7303425</v>
+        <v>7303586</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4521,12 +4486,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4541,44 +4511,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129411769</v>
+        <v>129411754</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4558,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>764796</v>
+        <v>764721</v>
       </c>
       <c r="R41" t="n">
-        <v>7303480</v>
+        <v>7303346</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4624,6 +4594,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>5×1m riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,10 +4625,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129411758</v>
+        <v>129411755</v>
       </c>
       <c r="B42" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4685,10 +4660,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>764675</v>
+        <v>764687</v>
       </c>
       <c r="R42" t="n">
-        <v>7303377</v>
+        <v>7303363</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4721,6 +4696,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2×2m mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4747,32 +4727,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129411770</v>
+        <v>129411756</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4762,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>764812</v>
+        <v>764666</v>
       </c>
       <c r="R43" t="n">
-        <v>7303506</v>
+        <v>7303358</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4818,6 +4798,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2×4m riklig förekomst</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4844,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129411763</v>
+        <v>129411757</v>
       </c>
       <c r="B44" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>764668</v>
+        <v>764671</v>
       </c>
       <c r="R44" t="n">
-        <v>7303401</v>
+        <v>7303368</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4915,11 +4900,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1×2m</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4946,32 +4926,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129411749</v>
+        <v>129411758</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4981,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>764687</v>
+        <v>764675</v>
       </c>
       <c r="R45" t="n">
-        <v>7303270</v>
+        <v>7303377</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5043,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129411757</v>
+        <v>129411759</v>
       </c>
       <c r="B46" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5081,7 +5061,7 @@
         <v>764671</v>
       </c>
       <c r="R46" t="n">
-        <v>7303368</v>
+        <v>7303388</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5114,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2×5m riklig förekomst</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5140,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129411762</v>
+        <v>129411760</v>
       </c>
       <c r="B47" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>764665</v>
+        <v>764659</v>
       </c>
       <c r="R47" t="n">
-        <v>7303417</v>
+        <v>7303400</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5211,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2×7m riklig förekomst</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5242,10 +5222,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129411765</v>
+        <v>129411761</v>
       </c>
       <c r="B48" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5277,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>764684</v>
+        <v>764651</v>
       </c>
       <c r="R48" t="n">
-        <v>7303436</v>
+        <v>7303425</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5313,11 +5293,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1×4 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129411760</v>
+        <v>129411762</v>
       </c>
       <c r="B49" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5379,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>764659</v>
+        <v>764665</v>
       </c>
       <c r="R49" t="n">
-        <v>7303400</v>
+        <v>7303417</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5415,6 +5390,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2×7m riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5441,32 +5421,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129411746</v>
+        <v>129411763</v>
       </c>
       <c r="B50" t="n">
-        <v>91610</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>764702</v>
+        <v>764668</v>
       </c>
       <c r="R50" t="n">
-        <v>7303366</v>
+        <v>7303401</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5512,6 +5492,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1×2m</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5538,32 +5523,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129411773</v>
+        <v>129411764</v>
       </c>
       <c r="B51" t="n">
-        <v>80221</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5573,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>764670</v>
+        <v>764686</v>
       </c>
       <c r="R51" t="n">
-        <v>7303409</v>
+        <v>7303430</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5609,6 +5594,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2×5 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5635,32 +5625,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129411752</v>
+        <v>129411765</v>
       </c>
       <c r="B52" t="n">
-        <v>80186</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>764672</v>
+        <v>764684</v>
       </c>
       <c r="R52" t="n">
-        <v>7303415</v>
+        <v>7303436</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5706,6 +5696,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1×4 m riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5732,45 +5727,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129411744</v>
+        <v>128509244</v>
       </c>
       <c r="B53" t="n">
-        <v>90631</v>
+        <v>97983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Granberget ö, Nb</t>
+          <t>granberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>764812</v>
+        <v>764534</v>
       </c>
       <c r="R53" t="n">
-        <v>7303485</v>
+        <v>7303539</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5797,12 +5792,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5829,32 +5824,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129411759</v>
+        <v>129411747</v>
       </c>
       <c r="B54" t="n">
-        <v>98780</v>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5864,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>764671</v>
+        <v>764824</v>
       </c>
       <c r="R54" t="n">
-        <v>7303388</v>
+        <v>7303549</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5904,7 +5899,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2×5m riklig förekomst</t>
+          <t>Mycket riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 40118-2025 artfynd.xlsx
+++ b/artfynd/A 40118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411746</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411744</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509251</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509252</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509254</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411767</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411769</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411770</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411743</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820678</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509245</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528442</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528443</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411749</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2529,6 +2624,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411750</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411751</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411752</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,6 +2930,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509243</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2917,6 +3032,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528440</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3014,6 +3134,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528441</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3120,6 +3245,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001075</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3217,6 +3347,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509255</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509256</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3420,6 +3560,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001074</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3517,6 +3662,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411773</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509246</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3711,6 +3866,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509248</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3813,6 +3973,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509250</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3915,6 +4080,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411753</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4012,6 +4182,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528439</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4118,6 +4293,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735620</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4220,6 +4400,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509247</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4317,6 +4502,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528444</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4414,6 +4604,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128528445</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4520,6 +4715,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001078</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4622,6 +4822,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411754</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4724,6 +4929,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411755</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4826,6 +5036,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411756</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4923,6 +5138,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411757</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5020,6 +5240,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411758</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5122,6 +5347,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411759</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5219,6 +5449,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411760</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5316,6 +5551,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411761</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5418,6 +5658,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411762</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5520,6 +5765,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411763</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5622,6 +5872,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411764</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5724,6 +5979,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411765</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5821,6 +6081,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128509244</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5923,8 +6188,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129411747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>